--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_300_R30.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_300_R30.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5674</v>
+        <v>4.3931</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7565</v>
+        <v>3.5822</v>
       </c>
       <c r="F2" t="n">
         <v>0.8109</v>
@@ -610,10 +610,10 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3383</v>
+        <v>0.4874</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4481</v>
+        <v>0.3776</v>
       </c>
       <c r="U2" t="n">
         <v>0.1098</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9321</v>
+        <v>2.0821</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4562</v>
+        <v>3.8415</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5241</v>
+        <v>-1.7593</v>
       </c>
       <c r="G3" t="n">
         <v>2.3289</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1419</v>
+        <v>0.2919</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0351</v>
+        <v>0.3501</v>
       </c>
       <c r="U3" t="n">
-        <v>0.177</v>
+        <v>-0.0582</v>
       </c>
       <c r="V3" t="n">
         <v>-1.4665</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6635</v>
+        <v>1.1603</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9153</v>
+        <v>1.8126</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5788</v>
+        <v>-0.6523</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6652</v>
+        <v>-0.1604</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9664</v>
+        <v>0.0168</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3012</v>
+        <v>-0.1772</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0691</v>
+        <v>2.188</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2163</v>
+        <v>1.4151</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472</v>
+        <v>0.7729</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4039</v>
+        <v>-2.3484</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2499</v>
+        <v>-1.3983</v>
       </c>
       <c r="O4" t="n">
-        <v>0.154</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3195</v>
+        <v>-2.7834</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5607</v>
+        <v>0.1041</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4732</v>
+        <v>0.2636</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.1595</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. JOSEPH</t>
+          <t>F. NTILIKINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2838</v>
+        <v>1.1461</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2747</v>
+        <v>0.7851</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5585</v>
+        <v>0.361</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.618</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6028</v>
+        <v>-0.3168</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5153</v>
+        <v>-0.3012</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.9944</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6953</v>
+        <v>0.9243</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.0701</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.175</v>
+        <v>-1.6123</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0926</v>
+        <v>-1.241</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2676</v>
+        <v>-0.3713</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0851</v>
+        <v>-0.2359</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9752</v>
+        <v>0.1103</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1098</v>
+        <v>-0.3462</v>
       </c>
       <c r="V5" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>C. JOSEPH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2126</v>
+        <v>1.0793</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6632</v>
+        <v>-0.4792</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4507</v>
+        <v>1.5585</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1604</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0168</v>
+        <v>-0.6028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1772</v>
+        <v>0.5153</v>
       </c>
       <c r="J6" t="n">
-        <v>2.188</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4151</v>
+        <v>-0.6953</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7729</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3484</v>
+        <v>-0.175</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3983</v>
+        <v>0.0926</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.2676</v>
       </c>
       <c r="P6" t="n">
         <v>-0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7834</v>
+        <v>-2.5515</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1564</v>
+        <v>0.8806</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1142</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0422</v>
+        <v>0.1098</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1444</v>
+        <v>1.214</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>1.214</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0162</v>
+        <v>0.761</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1418</v>
+        <v>0.8193</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1256</v>
+        <v>-0.0584</v>
       </c>
       <c r="G7" t="n">
         <v>2.9455</v>
@@ -1000,13 +1000,13 @@
         <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7486</v>
+        <v>0.4933</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1246</v>
+        <v>0.8022</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.376</v>
+        <v>-0.3088</v>
       </c>
       <c r="V7" t="n">
         <v>-1.7501</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. NTILIKINA</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1546</v>
+        <v>0.3638</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-2.1814</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2266</v>
+        <v>2.5452</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.618</v>
+        <v>-0.6652</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3168</v>
+        <v>-0.9664</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3012</v>
+        <v>0.3012</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9944</v>
+        <v>-1.0691</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9243</v>
+        <v>-1.2163</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0701</v>
+        <v>0.1472</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6123</v>
+        <v>0.4039</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.241</v>
+        <v>0.2499</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3713</v>
+        <v>0.154</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2274</v>
+        <v>1.261</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7468</v>
+        <v>1.2072</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4806</v>
+        <v>0.0538</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0647</v>
+        <v>-0.3599</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3408</v>
+        <v>-1.8376</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2761</v>
+        <v>1.4777</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2997</v>
@@ -1156,13 +1156,13 @@
         <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2469</v>
+        <v>0.458</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0395</v>
+        <v>0.5427</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2864</v>
+        <v>-0.0848</v>
       </c>
       <c r="V9" t="n">
         <v>0.3943</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9837</v>
+        <v>-1.7694</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3951</v>
+        <v>0.5759</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3788</v>
+        <v>-2.3452</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5475</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4336</v>
+        <v>-0.2192</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1142</v>
+        <v>0.295</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5478</v>
+        <v>-0.5142</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4665</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7565</v>
+        <v>-2.3376</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6652</v>
+        <v>-1.2799</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0577</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1451</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.127</v>
+        <v>0.2919</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1098</v>
+        <v>0.2754</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0171</v>
+        <v>0.0165</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2525</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.0253</v>
+        <v>6.518800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1448</v>
+        <v>5.638499999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0.8803999999999994</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2675999999999998</v>
+        <v>0.2676000000000003</v>
       </c>
       <c r="H12" t="n">
         <v>1.5726</v>
@@ -1381,7 +1381,7 @@
         <v>-3.9806</v>
       </c>
       <c r="P12" t="n">
-        <v>3.479200000000001</v>
+        <v>3.4792</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.2367</v>
@@ -1390,13 +1390,13 @@
         <v>19.7161</v>
       </c>
       <c r="S12" t="n">
-        <v>2.319500000000001</v>
+        <v>3.8131</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5011</v>
+        <v>4.994800000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1817</v>
+        <v>-1.1818</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0411</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9591</v>
+        <v>2.5989</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0128</v>
+        <v>3.4846</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0537</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-1.158</v>
@@ -1468,13 +1468,13 @@
         <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.973</v>
+        <v>-0.3332</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5816</v>
+        <v>-0.1098</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3914</v>
+        <v>-0.2234</v>
       </c>
       <c r="V13" t="n">
         <v>2.0026</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8966</v>
+        <v>1.5265</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2397</v>
+        <v>1.7853</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3431</v>
+        <v>-0.2588</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5318</v>
+        <v>-1.5101</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0131</v>
+        <v>-0.6601</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5187</v>
+        <v>-0.8499</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6325</v>
+        <v>0.7059</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7392</v>
+        <v>0.7597</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8932</v>
+        <v>-0.0538</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1007</v>
+        <v>-2.216</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7261</v>
+        <v>-1.4199</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3746</v>
+        <v>-0.7961</v>
       </c>
       <c r="P14" t="n">
+        <v>1.1598</v>
+      </c>
+      <c r="Q14" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2747</v>
+        <v>-0.1259</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9268</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3479</v>
+        <v>-0.2205</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.7501</v>
+        <v>2.0026</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7501</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0531</v>
+        <v>0.464</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3996</v>
+        <v>0.0458</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6535</v>
+        <v>0.4182</v>
       </c>
       <c r="G15" t="n">
         <v>0.0581</v>
@@ -1624,13 +1624,13 @@
         <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5311</v>
+        <v>-0.058</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4129</v>
+        <v>0.0591</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1182</v>
+        <v>-0.1171</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.4318</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9596</v>
+        <v>2.1781</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1244</v>
+        <v>-1.7464</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5101</v>
+        <v>2.5318</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6601</v>
+        <v>2.0131</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8499</v>
+        <v>0.5187</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7059</v>
+        <v>3.6325</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7597</v>
+        <v>2.7392</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0538</v>
+        <v>0.8932</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.216</v>
+        <v>-1.1007</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4199</v>
+        <v>-0.7261</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7961</v>
+        <v>-0.3746</v>
       </c>
       <c r="P16" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-2.3195</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.1598</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.1598</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.3195</v>
-      </c>
       <c r="S16" t="n">
-        <v>-0.8171</v>
+        <v>0.8098</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.731</v>
+        <v>0.8652</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0861</v>
+        <v>-0.0553</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0026</v>
+        <v>-1.7501</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1592</v>
+        <v>-0.4458</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6182</v>
+        <v>-0.9721</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4591</v>
+        <v>0.5263</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0805</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5605</v>
+        <v>-0.8472</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1098</v>
+        <v>-0.4637</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4507</v>
+        <v>-0.3835</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1418</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. HOLMES</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6811</v>
+        <v>-0.8565</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9553</v>
+        <v>-0.3607</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6364</v>
+        <v>-0.4958</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7018</v>
+        <v>3.7083</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0108</v>
+        <v>1.5736</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7126</v>
+        <v>2.1347</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0782</v>
+        <v>5.9671</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8942</v>
+        <v>2.5109</v>
       </c>
       <c r="L18" t="n">
-        <v>0.184</v>
+        <v>3.4561</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.78</v>
+        <v>-2.2587</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8834</v>
+        <v>-0.9373</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8966</v>
+        <v>-1.3215</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>-4.4071</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-6.9585</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3249</v>
+        <v>-0.6939</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4312</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1063</v>
+        <v>-0.7885</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3943</v>
+        <v>0.5361</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9361</v>
+        <v>-0.9025</v>
       </c>
       <c r="E19" t="n">
         <v>-1.2008</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2647</v>
+        <v>0.2984</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0307</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2095</v>
+        <v>-0.1759</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>R. HOLMES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7768</v>
+        <v>-1.3888</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1632</v>
+        <v>0.2476</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6137</v>
+        <v>-1.6364</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6907</v>
+        <v>-0.7018</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9389</v>
+        <v>0.0108</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6296</v>
+        <v>-0.7126</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0234</v>
+        <v>1.0782</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1912</v>
+        <v>0.8942</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2146</v>
+        <v>0.184</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3326</v>
+        <v>-1.78</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7477</v>
+        <v>-0.8834</v>
       </c>
       <c r="O20" t="n">
-        <v>0.415</v>
+        <v>-0.8966</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1634</v>
+        <v>0.6172</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6844</v>
+        <v>0.7235</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8478</v>
+        <v>-0.1063</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6083</v>
+        <v>-0.3943</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.2166</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0182</v>
+        <v>-2.0747</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1863</v>
+        <v>-2.7038</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8319</v>
+        <v>0.629</v>
       </c>
       <c r="G21" t="n">
-        <v>3.7083</v>
+        <v>-1.2629</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5736</v>
+        <v>-0.7911</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1347</v>
+        <v>-0.4718</v>
       </c>
       <c r="J21" t="n">
-        <v>5.9671</v>
+        <v>-1.5559</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5109</v>
+        <v>-0.7695</v>
       </c>
       <c r="L21" t="n">
-        <v>3.4561</v>
+        <v>-0.7863</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2587</v>
+        <v>0.293</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9373</v>
+        <v>-0.0216</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3215</v>
+        <v>0.3145</v>
       </c>
       <c r="P21" t="n">
-        <v>-4.4071</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-6.9585</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5515</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8556</v>
+        <v>0.116</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.731</v>
+        <v>0.0119</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1246</v>
+        <v>0.1041</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2434</v>
+        <v>-2.1814</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9397</v>
+        <v>-0.635</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6963</v>
+        <v>-1.5465</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2629</v>
+        <v>0.6907</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7911</v>
+        <v>-0.9389</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4718</v>
+        <v>1.6296</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5559</v>
+        <v>1.0234</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7695</v>
+        <v>-0.1912</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7863</v>
+        <v>1.2146</v>
       </c>
       <c r="M22" t="n">
-        <v>0.293</v>
+        <v>-0.3326</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0216</v>
+        <v>-0.7477</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3145</v>
+        <v>0.415</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R22" t="n">
-        <v>0.232</v>
+        <v>2.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0527</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.224</v>
+        <v>0.2126</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1713</v>
+        <v>-0.7806</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9544</v>
+        <v>-2.1966</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0171</v>
+        <v>-3.4274</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0627</v>
+        <v>1.2307</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5125</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8183</v>
+        <v>-1.0605</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8215</v>
+        <v>-0.2317</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9968</v>
+        <v>-0.8287</v>
       </c>
       <c r="V23" t="n">
         <v>1.0722</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0252</v>
+        <v>-5.0251</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.558300000000001</v>
+        <v>-1.5584</v>
       </c>
       <c r="F24" t="n">
         <v>-3.4669</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2675999999999998</v>
+        <v>-0.2676000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-1.5727</v>
@@ -2299,13 +2299,13 @@
         <v>1.3053</v>
       </c>
       <c r="J24" t="n">
-        <v>9.723000000000001</v>
+        <v>9.723000000000003</v>
       </c>
       <c r="K24" t="n">
-        <v>5.742300000000001</v>
+        <v>5.742299999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>3.9805</v>
+        <v>3.980500000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-9.990500000000001</v>
@@ -2326,13 +2326,13 @@
         <v>16.2368</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.3194</v>
+        <v>-2.3196</v>
       </c>
       <c r="T24" t="n">
-        <v>1.181700000000001</v>
+        <v>1.1818</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.5012</v>
+        <v>-3.5011</v>
       </c>
       <c r="V24" t="n">
         <v>1.0411</v>
